--- a/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-person.xlsx
+++ b/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-person.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1871" uniqueCount="382">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:13:23+00:00</t>
+    <t>2026-06-19T14:20:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -455,7 +455,7 @@
     <t>as-ext-person-birth-place</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-person-birth-place|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-person-birth-place|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -478,7 +478,7 @@
     <t>as-ext-person-deceased-date-time</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Person.deceasedDateTime|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Person.deceasedDateTime|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -542,7 +542,7 @@
     <t>Person.name</t>
   </si>
   <si>
-    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name|2.1.0}
+    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name|2.2.0}
 </t>
   </si>
   <si>
@@ -604,7 +604,7 @@
     <t>assemblyOrder</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {humanname-assembly-order|5.3.0}
+    <t xml:space="preserve">Extension {humanname-assembly-order|5.2.0}
 </t>
   </si>
   <si>
@@ -630,6 +630,9 @@
   </si>
   <si>
     <t>required</t>
+  </si>
+  <si>
+    <t>The use of a human name.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
@@ -736,10 +739,10 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>Civilités des personnes physiques du RASS</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J78-Civilite-RASS/FHIR/JDV-J78-Civilite-RASS|20221216120000</t>
+    <t>Civilités des personnes physiques</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J245-Civilite-CISIS/FHIR/JDV-J245-Civilite-CISIS|20230331120000</t>
   </si>
   <si>
     <t>HumanName.prefix</t>
@@ -757,16 +760,10 @@
     <t>Person.name.suffix</t>
   </si>
   <si>
-    <t>jeu de valeurs pour spécifier le titre de la personne</t>
+    <t>Parts that come after the name</t>
   </si>
   <si>
     <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the end of the name.</t>
-  </si>
-  <si>
-    <t>Civilités d'exercice d'un professionnel du RASS</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J79-CiviliteExercice-RASS/FHIR/JDV-J79-CiviliteExercice-RASS|20200424120000</t>
   </si>
   <si>
     <t>HumanName.suffix</t>
@@ -806,7 +803,7 @@
     <t>Person.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.1.0}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
 </t>
   </si>
   <si>
@@ -840,14 +837,16 @@
     <t>emailType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.2.0}
 </t>
   </si>
   <si>
     <t>Type of email | type de messagerie électronique</t>
   </si>
   <si>
-    <t>Extension on the ContactPoint datatype. This extension allows to specify the type of mail used to contact the person (MSSsanté|Apicrypt|OSM|Autre).</t>
+    <t>Extension permettant d'indiquer le type d'adresse email d'un ContactPoint.
++ This extension allows to specify the type of mail used to contact the person.</t>
   </si>
   <si>
     <t>Person.telecom.system</t>
@@ -1198,7 +1197,7 @@
     <t>Person.link:as-practitioner-exercice-professionnel.target</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-2)
 </t>
   </si>
   <si>
@@ -1532,7 +1531,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="87.8671875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="91.87890625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="80.25390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -3557,9 +3556,11 @@
       <c r="X18" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="Y18" s="2"/>
+      <c r="Y18" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="Z18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>77</v>
@@ -3577,7 +3578,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3595,21 +3596,21 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3635,16 +3636,16 @@
         <v>177</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3693,7 +3694,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3711,25 +3712,25 @@
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3751,13 +3752,13 @@
         <v>177</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3807,7 +3808,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3822,28 +3823,28 @@
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3865,13 +3866,13 @@
         <v>177</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3921,7 +3922,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3936,24 +3937,24 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3979,10 +3980,10 @@
         <v>177</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4009,13 +4010,13 @@
         <v>77</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>77</v>
@@ -4033,7 +4034,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4048,24 +4049,24 @@
         <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4091,10 +4092,10 @@
         <v>177</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4121,31 +4122,31 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>231</v>
+        <v>77</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>241</v>
+        <v>77</v>
       </c>
       <c r="Z23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4163,21 +4164,21 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>245</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4200,17 +4201,17 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4259,7 +4260,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4277,21 +4278,21 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>253</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4314,19 +4315,19 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4375,7 +4376,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4393,21 +4394,21 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>261</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4516,10 +4517,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4630,13 +4631,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="C28" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>77</v>
@@ -4658,13 +4659,13 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4744,10 +4745,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4773,10 +4774,10 @@
         <v>108</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4806,28 +4807,28 @@
         <v>197</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="Z29" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="Z29" t="s" s="2">
+      <c r="AA29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4836,7 +4837,7 @@
         <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>100</v>
@@ -4845,21 +4846,21 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>277</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4885,16 +4886,16 @@
         <v>177</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4943,7 +4944,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4961,21 +4962,21 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>285</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5001,16 +5002,16 @@
         <v>108</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5038,28 +5039,28 @@
         <v>197</v>
       </c>
       <c r="Y31" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="Z31" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z31" t="s" s="2">
+      <c r="AA31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5077,21 +5078,21 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5114,16 +5115,16 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5173,7 +5174,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5202,10 +5203,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5228,13 +5229,13 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5285,7 +5286,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5303,7 +5304,7 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5314,10 +5315,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5343,16 +5344,16 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5380,11 +5381,11 @@
         <v>197</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="Z34" t="s" s="2">
-        <v>311</v>
-      </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
       </c>
@@ -5401,7 +5402,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5416,24 +5417,24 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>314</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5456,19 +5457,19 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5517,7 +5518,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5532,24 +5533,24 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>323</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5572,19 +5573,19 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5633,7 +5634,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5651,21 +5652,21 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>331</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5688,13 +5689,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5745,7 +5746,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5763,21 +5764,21 @@
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>337</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5800,17 +5801,17 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -5859,7 +5860,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5877,7 +5878,7 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -5888,10 +5889,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5914,17 +5915,17 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5973,7 +5974,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5991,10 +5992,10 @@
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6002,10 +6003,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6028,13 +6029,13 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6073,7 +6074,7 @@
         <v>77</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -6083,7 +6084,7 @@
         <v>137</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6101,7 +6102,7 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6112,10 +6113,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6224,10 +6225,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6338,14 +6339,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6367,10 +6368,10 @@
         <v>133</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>157</v>
@@ -6425,7 +6426,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6454,10 +6455,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6480,13 +6481,13 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6537,7 +6538,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>88</v>
@@ -6555,7 +6556,7 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6566,10 +6567,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6595,10 +6596,10 @@
         <v>108</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6628,11 +6629,11 @@
         <v>197</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="Z45" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AA45" t="s" s="2">
         <v>77</v>
       </c>
@@ -6649,7 +6650,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6667,7 +6668,7 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6678,13 +6679,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="C46" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>77</v>
@@ -6706,13 +6707,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6763,7 +6764,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6781,7 +6782,7 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6792,10 +6793,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6904,10 +6905,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7018,14 +7019,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7047,10 +7048,10 @@
         <v>133</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>157</v>
@@ -7105,7 +7106,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7134,10 +7135,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7160,13 +7161,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7217,7 +7218,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>88</v>
@@ -7235,7 +7236,7 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7246,10 +7247,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7275,10 +7276,10 @@
         <v>108</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7308,11 +7309,11 @@
         <v>197</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7329,7 +7330,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7347,7 +7348,7 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>

--- a/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-person.xlsx
+++ b/www/ig/fhir/annuaire/1.2.0-snapshot-1/StructureDefinition-as-person.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1871" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="383">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:20:56+00:00</t>
+    <t>2026-06-16T14:13:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -455,7 +455,7 @@
     <t>as-ext-person-birth-place</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-person-birth-place|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-person-birth-place|1.2.0-snapshot-1}
 </t>
   </si>
   <si>
@@ -478,7 +478,7 @@
     <t>as-ext-person-deceased-date-time</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Person.deceasedDateTime|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-Person.deceasedDateTime|1.2.0-snapshot-1}
 </t>
   </si>
   <si>
@@ -542,7 +542,7 @@
     <t>Person.name</t>
   </si>
   <si>
-    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name|2.2.0}
+    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name|2.1.0}
 </t>
   </si>
   <si>
@@ -604,7 +604,7 @@
     <t>assemblyOrder</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {humanname-assembly-order|5.2.0}
+    <t xml:space="preserve">Extension {humanname-assembly-order|5.3.0}
 </t>
   </si>
   <si>
@@ -630,9 +630,6 @@
   </si>
   <si>
     <t>required</t>
-  </si>
-  <si>
-    <t>The use of a human name.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
@@ -739,10 +736,10 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>Civilités des personnes physiques</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J245-Civilite-CISIS/FHIR/JDV-J245-Civilite-CISIS|20230331120000</t>
+    <t>Civilités des personnes physiques du RASS</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J78-Civilite-RASS/FHIR/JDV-J78-Civilite-RASS|20221216120000</t>
   </si>
   <si>
     <t>HumanName.prefix</t>
@@ -760,10 +757,16 @@
     <t>Person.name.suffix</t>
   </si>
   <si>
-    <t>Parts that come after the name</t>
+    <t>jeu de valeurs pour spécifier le titre de la personne</t>
   </si>
   <si>
     <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the end of the name.</t>
+  </si>
+  <si>
+    <t>Civilités d'exercice d'un professionnel du RASS</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J79-CiviliteExercice-RASS/FHIR/JDV-J79-CiviliteExercice-RASS|20200424120000</t>
   </si>
   <si>
     <t>HumanName.suffix</t>
@@ -803,7 +806,7 @@
     <t>Person.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.1.0}
 </t>
   </si>
   <si>
@@ -837,16 +840,14 @@
     <t>emailType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.2.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.1.0}
 </t>
   </si>
   <si>
     <t>Type of email | type de messagerie électronique</t>
   </si>
   <si>
-    <t>Extension permettant d'indiquer le type d'adresse email d'un ContactPoint.
-- This extension allows to specify the type of mail used to contact the person.</t>
+    <t>Extension on the ContactPoint datatype. This extension allows to specify the type of mail used to contact the person (MSSsanté|Apicrypt|OSM|Autre).</t>
   </si>
   <si>
     <t>Person.telecom.system</t>
@@ -1197,7 +1198,7 @@
     <t>Person.link:as-practitioner-exercice-professionnel.target</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-2)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-1)
 </t>
   </si>
   <si>
@@ -1531,7 +1532,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="87.8671875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="80.25390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="91.87890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -3556,29 +3557,27 @@
       <c r="X18" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="Y18" t="s" s="2">
+      <c r="Y18" s="2"/>
+      <c r="Z18" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z18" t="s" s="2">
+      <c r="AA18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3596,21 +3595,21 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>202</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3636,16 +3635,16 @@
         <v>177</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3694,7 +3693,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3712,25 +3711,25 @@
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>210</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3752,13 +3751,13 @@
         <v>177</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3808,7 +3807,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3823,28 +3822,28 @@
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AM20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>219</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3866,13 +3865,13 @@
         <v>177</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3922,7 +3921,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3937,24 +3936,24 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AM21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>228</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3980,10 +3979,10 @@
         <v>177</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4010,31 +4009,31 @@
         <v>77</v>
       </c>
       <c r="X22" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="Y22" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="Y22" t="s" s="2">
+      <c r="Z22" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="Z22" t="s" s="2">
+      <c r="AA22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4049,24 +4048,24 @@
         <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>238</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4092,10 +4091,10 @@
         <v>177</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4122,13 +4121,13 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>77</v>
+        <v>231</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>77</v>
+        <v>241</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>77</v>
+        <v>242</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
@@ -4146,7 +4145,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4164,21 +4163,21 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4201,17 +4200,17 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4260,7 +4259,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4278,21 +4277,21 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4315,19 +4314,19 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4376,7 +4375,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4394,21 +4393,21 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4517,10 +4516,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4631,13 +4630,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="B28" t="s" s="2">
-        <v>262</v>
-      </c>
       <c r="C28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>77</v>
@@ -4659,13 +4658,13 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4745,10 +4744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4774,10 +4773,10 @@
         <v>108</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4807,10 +4806,10 @@
         <v>197</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -4828,7 +4827,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4837,7 +4836,7 @@
         <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>100</v>
@@ -4846,21 +4845,21 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4886,16 +4885,16 @@
         <v>177</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4944,7 +4943,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4962,21 +4961,21 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5002,16 +5001,16 @@
         <v>108</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5039,10 +5038,10 @@
         <v>197</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -5060,7 +5059,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5078,21 +5077,21 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5115,16 +5114,16 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5174,7 +5173,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5203,10 +5202,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5229,13 +5228,13 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5286,7 +5285,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5304,7 +5303,7 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5315,10 +5314,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5344,16 +5343,16 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5381,10 +5380,10 @@
         <v>197</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5402,7 +5401,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5417,24 +5416,24 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5457,19 +5456,19 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5518,7 +5517,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5533,24 +5532,24 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5573,19 +5572,19 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5634,7 +5633,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5652,21 +5651,21 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5689,13 +5688,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5746,7 +5745,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5764,21 +5763,21 @@
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5801,17 +5800,17 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -5860,7 +5859,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5878,7 +5877,7 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -5889,10 +5888,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5915,17 +5914,17 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5974,7 +5973,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5992,10 +5991,10 @@
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6003,10 +6002,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6029,13 +6028,13 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6074,7 +6073,7 @@
         <v>77</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -6084,7 +6083,7 @@
         <v>137</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6102,7 +6101,7 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6113,10 +6112,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6225,10 +6224,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6339,14 +6338,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6368,10 +6367,10 @@
         <v>133</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>157</v>
@@ -6426,7 +6425,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6455,10 +6454,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6481,13 +6480,13 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6538,7 +6537,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>88</v>
@@ -6556,7 +6555,7 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6567,10 +6566,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6596,10 +6595,10 @@
         <v>108</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6629,10 +6628,10 @@
         <v>197</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>77</v>
@@ -6650,7 +6649,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6668,7 +6667,7 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6679,13 +6678,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>77</v>
@@ -6707,13 +6706,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6764,7 +6763,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6782,7 +6781,7 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6793,10 +6792,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6905,10 +6904,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7019,14 +7018,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7048,10 +7047,10 @@
         <v>133</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>157</v>
@@ -7106,7 +7105,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7135,10 +7134,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7161,13 +7160,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7218,7 +7217,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>88</v>
@@ -7236,7 +7235,7 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7247,10 +7246,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7276,10 +7275,10 @@
         <v>108</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7309,10 +7308,10 @@
         <v>197</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -7330,7 +7329,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7348,7 +7347,7 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
